--- a/data/trans_dic/P6906-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,59; 52,57</t>
+          <t>20,21; 50,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,15; 64,17</t>
+          <t>29,87; 62,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 52,2</t>
+          <t>23,18; 49,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 46,23</t>
+          <t>8,19; 48,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 49,75</t>
+          <t>11,68; 48,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 64,43</t>
+          <t>21,44; 60,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,99; 62,42</t>
+          <t>30,68; 61,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 58,04</t>
+          <t>19,41; 59,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,11; 45,27</t>
+          <t>21,48; 45,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,96; 56,15</t>
+          <t>32,63; 57,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 51,32</t>
+          <t>31,44; 51,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 44,98</t>
+          <t>16,0; 44,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 35,31</t>
+          <t>13,47; 37,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 44,45</t>
+          <t>18,81; 43,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 27,91</t>
+          <t>8,12; 25,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 48,88</t>
+          <t>13,58; 48,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 36,18</t>
+          <t>8,53; 33,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,36; 38,32</t>
+          <t>8,81; 41,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 41,69</t>
+          <t>14,8; 42,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 48,18</t>
+          <t>23,51; 49,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 31,92</t>
+          <t>13,37; 32,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 36,38</t>
+          <t>17,42; 36,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 27,84</t>
+          <t>12,84; 27,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 43,62</t>
+          <t>22,59; 43,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 35,52</t>
+          <t>5,49; 33,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 46,2</t>
+          <t>11,61; 46,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,52</t>
+          <t>0,0; 20,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 28,77</t>
+          <t>6,88; 26,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 36,66</t>
+          <t>4,61; 32,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 50,31</t>
+          <t>10,36; 52,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,05</t>
+          <t>0,0; 51,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,51; 35,77</t>
+          <t>15,56; 35,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 30,23</t>
+          <t>7,08; 28,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 40,38</t>
+          <t>15,73; 41,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,56</t>
+          <t>0,0; 25,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 26,84</t>
+          <t>12,71; 26,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 32,92</t>
+          <t>9,99; 33,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 46,14</t>
+          <t>17,04; 44,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,47; 64,8</t>
+          <t>29,08; 65,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 51,14</t>
+          <t>13,58; 50,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,95</t>
+          <t>0,0; 28,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 56,89</t>
+          <t>18,85; 55,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 60,49</t>
+          <t>26,5; 58,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 39,66</t>
+          <t>5,88; 39,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 26,59</t>
+          <t>9,73; 27,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 44,17</t>
+          <t>22,42; 44,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 57,88</t>
+          <t>33,51; 58,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 37,7</t>
+          <t>10,41; 37,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 28,88</t>
+          <t>3,59; 31,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,77</t>
+          <t>0,0; 31,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 66,49</t>
+          <t>12,25; 67,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 26,77</t>
+          <t>2,98; 28,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,14</t>
+          <t>0,0; 58,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 58,87</t>
+          <t>7,01; 58,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,37</t>
+          <t>0,0; 83,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 25,3</t>
+          <t>1,42; 26,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 28,95</t>
+          <t>3,2; 29,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 30,63</t>
+          <t>3,61; 29,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,0; 60,0</t>
+          <t>12,3; 59,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 21,44</t>
+          <t>4,23; 21,24</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 36,28</t>
+          <t>9,79; 37,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 29,18</t>
+          <t>6,64; 29,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,04</t>
+          <t>0,0; 23,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 31,46</t>
+          <t>7,39; 31,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,3</t>
+          <t>0,0; 44,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 62,53</t>
+          <t>12,65; 61,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 88,82</t>
+          <t>20,25; 88,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,82; 40,37</t>
+          <t>16,03; 42,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 33,23</t>
+          <t>10,9; 31,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 31,64</t>
+          <t>11,68; 32,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 37,17</t>
+          <t>9,7; 41,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,49; 31,26</t>
+          <t>12,96; 30,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,9; 28,36</t>
+          <t>10,1; 26,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,38; 37,73</t>
+          <t>14,38; 39,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 30,18</t>
+          <t>10,48; 29,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 29,34</t>
+          <t>10,44; 31,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,41; 42,86</t>
+          <t>15,22; 43,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 43,73</t>
+          <t>16,64; 42,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 37,23</t>
+          <t>15,26; 39,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,17; 43,39</t>
+          <t>23,24; 42,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 28,5</t>
+          <t>13,87; 28,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 35,85</t>
+          <t>17,78; 35,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,73; 29,19</t>
+          <t>14,44; 29,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,53; 32,92</t>
+          <t>19,29; 33,03</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,35; 36,58</t>
+          <t>19,79; 35,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 28,74</t>
+          <t>4,93; 29,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,7; 45,54</t>
+          <t>15,46; 45,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 19,53</t>
+          <t>3,45; 19,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,33; 43,65</t>
+          <t>16,93; 43,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,96; 49,22</t>
+          <t>10,48; 47,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 47,28</t>
+          <t>6,34; 46,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 24,86</t>
+          <t>6,9; 24,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,18; 35,17</t>
+          <t>20,46; 34,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,44; 31,04</t>
+          <t>11,27; 31,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 40,0</t>
+          <t>16,15; 40,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 18,85</t>
+          <t>6,42; 18,67</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,87</t>
+          <t>18,99; 26,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,88; 31,09</t>
+          <t>21,21; 30,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,25; 29,12</t>
+          <t>19,04; 28,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,76; 24,42</t>
+          <t>14,51; 24,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,49</t>
+          <t>16,43; 28,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,69; 36,26</t>
+          <t>23,59; 36,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,65; 39,62</t>
+          <t>25,81; 38,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,18; 29,99</t>
+          <t>18,01; 29,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,67</t>
+          <t>19,12; 25,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,42</t>
+          <t>23,79; 31,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,8; 31,32</t>
+          <t>23,44; 31,28</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,36; 26,11</t>
+          <t>18,49; 25,62</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9252; 22524</t>
+          <t>8658; 21793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12575; 25907</t>
+          <t>12061; 25342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13945; 30580</t>
+          <t>13580; 28975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1949; 11127</t>
+          <t>1972; 11596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3720; 14238</t>
+          <t>3341; 13786</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6741; 18783</t>
+          <t>6249; 17674</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12669; 25520</t>
+          <t>12544; 25036</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3275; 9145</t>
+          <t>3058; 9316</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15801; 32348</t>
+          <t>15352; 32230</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22219; 39041</t>
+          <t>22684; 40133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29998; 51039</t>
+          <t>31269; 51606</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7078; 17911</t>
+          <t>6370; 17868</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9347; 25563</t>
+          <t>9749; 26834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10720; 25155</t>
+          <t>10645; 24557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7492; 23109</t>
+          <t>6725; 21188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6099; 22621</t>
+          <t>6284; 22251</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2760; 11828</t>
+          <t>2788; 11048</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2869; 13149</t>
+          <t>3024; 14121</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6812; 17801</t>
+          <t>6319; 18096</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10297; 21895</t>
+          <t>10683; 22395</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14494; 33546</t>
+          <t>14053; 33753</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16767; 33073</t>
+          <t>15840; 33520</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16496; 34931</t>
+          <t>16118; 35059</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20337; 40008</t>
+          <t>20721; 39814</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2002; 13005</t>
+          <t>2010; 12178</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2967; 11692</t>
+          <t>2937; 11677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3725</t>
+          <t>0; 4461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3632; 14239</t>
+          <t>3407; 13158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1002; 7964</t>
+          <t>1001; 7081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1860; 9022</t>
+          <t>1858; 9350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6757</t>
+          <t>0; 6497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6664; 16429</t>
+          <t>7145; 16364</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4738; 17634</t>
+          <t>4131; 16886</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5863; 17462</t>
+          <t>6803; 17831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 8627</t>
+          <t>0; 8521</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12125; 25610</t>
+          <t>12128; 25732</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6141; 19197</t>
+          <t>5826; 19714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7734; 20698</t>
+          <t>7644; 20018</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9243; 21038</t>
+          <t>9442; 21361</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5800; 20637</t>
+          <t>5478; 20479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7028</t>
+          <t>0; 6401</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5570; 16801</t>
+          <t>5566; 16300</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7355; 18108</t>
+          <t>7933; 17570</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5406; 31987</t>
+          <t>4744; 31695</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7567; 21544</t>
+          <t>7880; 22272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17477; 32859</t>
+          <t>16681; 33226</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19505; 36117</t>
+          <t>20912; 36484</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12044; 45622</t>
+          <t>12595; 44848</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>832; 6628</t>
+          <t>823; 7287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4975</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1643; 9887</t>
+          <t>1821; 9994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>500; 4754</t>
+          <t>529; 5117</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4052</t>
+          <t>0; 4047</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>782; 6864</t>
+          <t>817; 6844</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>176; 2779</t>
+          <t>156; 2870</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>914; 8664</t>
+          <t>957; 8961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>983; 8524</t>
+          <t>1005; 8300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3097; 12386</t>
+          <t>2539; 12216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1133; 6163</t>
+          <t>1217; 6106</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3909; 15170</t>
+          <t>4094; 15808</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2956; 12659</t>
+          <t>2881; 12736</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6067</t>
+          <t>0; 5307</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1925; 9947</t>
+          <t>2336; 9802</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6102</t>
+          <t>0; 6213</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1936; 9495</t>
+          <t>1921; 9346</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1196; 6597</t>
+          <t>1504; 6598</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4479; 12198</t>
+          <t>4844; 12692</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5962; 18576</t>
+          <t>6092; 17416</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6856; 18531</t>
+          <t>6843; 18957</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2153; 11100</t>
+          <t>2896; 12254</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8343; 19331</t>
+          <t>8011; 18774</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9643; 25080</t>
+          <t>8938; 23286</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7284; 20534</t>
+          <t>7825; 21448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7872; 23647</t>
+          <t>8211; 23275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7280; 21473</t>
+          <t>7639; 23187</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6710; 18659</t>
+          <t>6624; 19062</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7901; 20282</t>
+          <t>7716; 19914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7964; 20730</t>
+          <t>8499; 21979</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17050; 30601</t>
+          <t>16393; 29946</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17803; 37620</t>
+          <t>18310; 37578</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17422; 36137</t>
+          <t>17925; 35939</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19743; 39117</t>
+          <t>19351; 39733</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28061; 47311</t>
+          <t>27717; 47472</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21072; 39843</t>
+          <t>21550; 38872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2262; 12969</t>
+          <t>2223; 13292</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6168; 17884</t>
+          <t>6072; 17960</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2073; 11085</t>
+          <t>1960; 11156</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8626; 21730</t>
+          <t>8431; 21750</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3362; 15098</t>
+          <t>3213; 14704</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1064; 10118</t>
+          <t>1357; 9899</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3677; 13600</t>
+          <t>3773; 13381</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33605; 55816</t>
+          <t>32463; 55408</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8671; 23523</t>
+          <t>8540; 23804</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9544; 24269</t>
+          <t>9800; 24437</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7302; 21013</t>
+          <t>7156; 20814</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>88075; 126925</t>
+          <t>89686; 126337</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>68102; 101429</t>
+          <t>69182; 100999</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67365; 101921</t>
+          <t>66641; 100637</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50125; 82915</t>
+          <t>49279; 82439</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36699; 60513</t>
+          <t>36169; 62153</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50884; 77900</t>
+          <t>50686; 78378</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>57639; 85697</t>
+          <t>55820; 83491</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64394; 106237</t>
+          <t>63793; 106128</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>133854; 177728</t>
+          <t>132408; 178065</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>127966; 169978</t>
+          <t>128695; 172629</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>134773; 177346</t>
+          <t>132743; 177122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>127376; 181106</t>
+          <t>128239; 177729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6906-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 50,87</t>
+          <t>21,02; 53,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,87; 62,77</t>
+          <t>30,97; 62,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,18; 49,46</t>
+          <t>24,41; 50,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 48,18</t>
+          <t>7,22; 39,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 48,17</t>
+          <t>11,51; 49,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,44; 60,63</t>
+          <t>21,57; 60,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,68; 61,24</t>
+          <t>29,44; 61,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 59,13</t>
+          <t>18,73; 54,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,48; 45,1</t>
+          <t>20,82; 43,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,63; 57,72</t>
+          <t>32,08; 56,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,44; 51,89</t>
+          <t>30,87; 51,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,0; 44,87</t>
+          <t>14,9; 37,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 37,07</t>
+          <t>12,38; 36,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 43,39</t>
+          <t>19,12; 43,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 25,59</t>
+          <t>9,02; 26,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,58; 48,08</t>
+          <t>17,04; 50,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 33,8</t>
+          <t>6,07; 33,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 41,15</t>
+          <t>8,82; 38,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 42,38</t>
+          <t>14,32; 41,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,51; 49,28</t>
+          <t>24,0; 47,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 32,12</t>
+          <t>12,78; 31,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 36,87</t>
+          <t>17,4; 36,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,84; 27,94</t>
+          <t>12,73; 26,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,59; 43,41</t>
+          <t>23,66; 44,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 33,26</t>
+          <t>7,32; 36,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 46,14</t>
+          <t>11,39; 45,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,99</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 26,58</t>
+          <t>7,3; 27,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 32,6</t>
+          <t>4,63; 37,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 52,13</t>
+          <t>10,52; 51,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,97</t>
+          <t>0,0; 53,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,56; 35,63</t>
+          <t>14,58; 34,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 28,94</t>
+          <t>6,96; 29,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 41,24</t>
+          <t>15,56; 40,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,24</t>
+          <t>0,0; 24,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 26,97</t>
+          <t>12,84; 26,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 33,8</t>
+          <t>10,28; 32,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 44,62</t>
+          <t>18,87; 47,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,08; 65,8</t>
+          <t>28,94; 66,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 50,75</t>
+          <t>18,02; 57,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,19</t>
+          <t>0,0; 28,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 55,19</t>
+          <t>19,45; 54,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,5; 58,69</t>
+          <t>26,18; 61,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 39,3</t>
+          <t>24,18; 47,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 27,49</t>
+          <t>9,91; 27,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 44,66</t>
+          <t>21,95; 44,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,51; 58,47</t>
+          <t>33,07; 58,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 37,06</t>
+          <t>25,09; 48,03</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 31,74</t>
+          <t>3,52; 33,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,23</t>
+          <t>0,0; 31,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 67,21</t>
+          <t>12,99; 68,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 28,82</t>
+          <t>2,57; 23,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,07</t>
+          <t>0,0; 69,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 58,69</t>
+          <t>6,74; 62,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,7</t>
+          <t>0,0; 84,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 26,13</t>
+          <t>2,89; 24,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,95</t>
+          <t>2,96; 28,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 29,83</t>
+          <t>3,56; 32,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,3; 59,18</t>
+          <t>14,76; 59,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 21,24</t>
+          <t>3,71; 19,58</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,79; 37,81</t>
+          <t>9,97; 35,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 29,36</t>
+          <t>7,04; 28,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,66</t>
+          <t>0,0; 25,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 31,0</t>
+          <t>6,89; 28,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,08</t>
+          <t>0,0; 44,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 61,55</t>
+          <t>13,21; 60,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,25; 88,83</t>
+          <t>24,94; 88,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,03; 42,0</t>
+          <t>13,95; 40,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,9; 31,15</t>
+          <t>9,23; 31,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,68; 32,37</t>
+          <t>12,13; 33,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 41,04</t>
+          <t>9,09; 38,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,96; 30,36</t>
+          <t>12,36; 28,93</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,33</t>
+          <t>10,16; 26,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,38; 39,4</t>
+          <t>13,16; 38,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 29,71</t>
+          <t>9,98; 29,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 31,69</t>
+          <t>13,24; 34,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 43,79</t>
+          <t>14,19; 40,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 42,94</t>
+          <t>16,68; 42,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,26; 39,47</t>
+          <t>15,09; 39,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,24; 42,46</t>
+          <t>25,09; 43,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,47</t>
+          <t>14,66; 27,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 35,65</t>
+          <t>18,0; 36,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 29,65</t>
+          <t>15,4; 30,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,29; 33,03</t>
+          <t>20,78; 34,93</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,79; 35,69</t>
+          <t>19,14; 36,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 29,46</t>
+          <t>6,94; 29,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,46; 45,73</t>
+          <t>15,92; 45,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 19,66</t>
+          <t>3,38; 19,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,93; 43,69</t>
+          <t>17,76; 41,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,48; 47,94</t>
+          <t>10,36; 49,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 46,26</t>
+          <t>5,29; 45,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,9; 24,46</t>
+          <t>6,89; 24,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,46; 34,91</t>
+          <t>20,98; 35,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 31,41</t>
+          <t>11,16; 31,09</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,15; 40,28</t>
+          <t>15,69; 39,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 18,67</t>
+          <t>6,62; 17,96</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,75</t>
+          <t>18,68; 26,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,21; 30,96</t>
+          <t>21,5; 31,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,75</t>
+          <t>19,45; 29,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,28</t>
+          <t>15,29; 24,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,43; 28,24</t>
+          <t>16,67; 27,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,48</t>
+          <t>23,1; 35,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,6</t>
+          <t>26,98; 39,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,01; 29,96</t>
+          <t>23,65; 32,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,72</t>
+          <t>19,21; 25,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,91</t>
+          <t>23,55; 31,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,28</t>
+          <t>23,64; 31,07</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,49; 25,62</t>
+          <t>20,75; 27,36</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>10626</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8658; 21793</t>
+          <t>9004; 22747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12061; 25342</t>
+          <t>12502; 25250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13580; 28975</t>
+          <t>14301; 29414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1972; 11596</t>
+          <t>1894; 10294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3341; 13786</t>
+          <t>3293; 14231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6249; 17674</t>
+          <t>6287; 17626</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12544; 25036</t>
+          <t>12037; 25165</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3058; 9316</t>
+          <t>3035; 8753</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15352; 32230</t>
+          <t>14878; 31419</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22684; 40133</t>
+          <t>22301; 39247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31269; 51606</t>
+          <t>30704; 51409</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6370; 17868</t>
+          <t>6322; 15894</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>31139</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9749; 26834</t>
+          <t>8963; 26343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10645; 24557</t>
+          <t>10821; 24579</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6725; 21188</t>
+          <t>7469; 21656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6284; 22251</t>
+          <t>8182; 24027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2788; 11048</t>
+          <t>1985; 10881</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3024; 14121</t>
+          <t>3025; 13045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6319; 18096</t>
+          <t>6115; 17525</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10683; 22395</t>
+          <t>11161; 22105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14053; 33753</t>
+          <t>13432; 32915</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15840; 33520</t>
+          <t>15815; 33210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16118; 35059</t>
+          <t>15976; 33760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20721; 39814</t>
+          <t>22366; 41935</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18503</t>
+          <t>18605</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2010; 12178</t>
+          <t>2680; 13187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2937; 11677</t>
+          <t>2883; 11479</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3407; 13158</t>
+          <t>3623; 13671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1001; 7081</t>
+          <t>1006; 8041</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1858; 9350</t>
+          <t>1887; 9313</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6497</t>
+          <t>0; 6712</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7145; 16364</t>
+          <t>6848; 16319</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4131; 16886</t>
+          <t>4059; 17240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6803; 17831</t>
+          <t>6730; 17567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 8521</t>
+          <t>0; 8229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12128; 25732</t>
+          <t>12400; 25940</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>37019</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5826; 19714</t>
+          <t>5996; 18725</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7644; 20018</t>
+          <t>8465; 21254</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9442; 21361</t>
+          <t>9397; 21715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5478; 20479</t>
+          <t>9759; 31010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6401</t>
+          <t>0; 6499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5566; 16300</t>
+          <t>5743; 16096</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7933; 17570</t>
+          <t>7836; 18434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4744; 31695</t>
+          <t>12885; 25549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7880; 22272</t>
+          <t>8031; 22379</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16681; 33226</t>
+          <t>16332; 33180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20912; 36484</t>
+          <t>20637; 36331</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12595; 44848</t>
+          <t>26957; 51606</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3385</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>823; 7287</t>
+          <t>807; 7581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5050</t>
+          <t>0; 5064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1821; 9994</t>
+          <t>1931; 10182</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>529; 5117</t>
+          <t>556; 5162</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4047</t>
+          <t>0; 4859</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>817; 6844</t>
+          <t>786; 7326</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4830</t>
+          <t>0; 4855</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>156; 2870</t>
+          <t>393; 3372</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>957; 8961</t>
+          <t>886; 8569</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1005; 8300</t>
+          <t>990; 8921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2539; 12216</t>
+          <t>3047; 12229</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1217; 6106</t>
+          <t>1309; 6902</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12774</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4094; 15808</t>
+          <t>4167; 14814</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2881; 12736</t>
+          <t>3056; 12255</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>0; 5810</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2336; 9802</t>
+          <t>2265; 9422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6213</t>
+          <t>0; 6326</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1921; 9346</t>
+          <t>2006; 9238</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1504; 6598</t>
+          <t>1852; 6604</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4844; 12692</t>
+          <t>4265; 12237</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6092; 17416</t>
+          <t>5160; 17713</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6843; 18957</t>
+          <t>7103; 19644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2896; 12254</t>
+          <t>2714; 11558</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8011; 18774</t>
+          <t>7840; 18359</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>45650</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8938; 23286</t>
+          <t>8990; 23713</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7825; 21448</t>
+          <t>7165; 21195</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8211; 23275</t>
+          <t>7821; 23121</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7639; 23187</t>
+          <t>11370; 29738</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6624; 19062</t>
+          <t>6179; 17799</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7716; 19914</t>
+          <t>7735; 19920</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8499; 21979</t>
+          <t>8400; 21975</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16393; 29946</t>
+          <t>20249; 35423</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18310; 37578</t>
+          <t>19352; 36928</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17925; 35939</t>
+          <t>18146; 36486</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19351; 39733</t>
+          <t>20637; 40455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27717; 47472</t>
+          <t>34607; 58190</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>14296</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21550; 38872</t>
+          <t>20842; 39869</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2223; 13292</t>
+          <t>3129; 13362</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6072; 17960</t>
+          <t>6252; 17824</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1960; 11156</t>
+          <t>2251; 13059</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8431; 21750</t>
+          <t>8844; 20758</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3213; 14704</t>
+          <t>3178; 15083</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1357; 9899</t>
+          <t>1132; 9664</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3773; 13381</t>
+          <t>3962; 13906</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32463; 55408</t>
+          <t>33288; 56041</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8540; 23804</t>
+          <t>8460; 23567</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9800; 24437</t>
+          <t>9520; 24138</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7156; 20814</t>
+          <t>8222; 22296</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>173494</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>89686; 126337</t>
+          <t>88246; 126617</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69182; 100999</t>
+          <t>70136; 102828</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66641; 100637</t>
+          <t>68077; 101494</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49279; 82439</t>
+          <t>58875; 94842</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36169; 62153</t>
+          <t>36686; 60996</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>50686; 78378</t>
+          <t>49624; 77038</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55820; 83491</t>
+          <t>58361; 85372</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>63793; 106128</t>
+          <t>81681; 111908</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>132408; 178065</t>
+          <t>133037; 179563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>128695; 172629</t>
+          <t>127406; 169802</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132743; 177122</t>
+          <t>133864; 175950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>128239; 177729</t>
+          <t>151571; 199855</t>
         </is>
       </c>
     </row>
